--- a/docs/SLMS2026_v2_nhieu_can_nha.xlsx
+++ b/docs/SLMS2026_v2_nhieu_can_nha.xlsx
@@ -1330,7 +1330,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I37"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1941,9 +1941,473 @@
         <v>Máy giặt sấy tích hợp</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>HD-HCM-ROOM-RENO-01</v>
+      </c>
+      <c r="B22" t="str">
+        <v>104</v>
+      </c>
+      <c r="C22" t="str">
+        <v/>
+      </c>
+      <c r="D22" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E22" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F22" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>HD-HCM-ROOM-RENO-01</v>
+      </c>
+      <c r="B23" t="str">
+        <v>105</v>
+      </c>
+      <c r="C23" t="str">
+        <v/>
+      </c>
+      <c r="D23" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E23" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F23" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>HD-HCM-ROOM-RENO-01</v>
+      </c>
+      <c r="B24" t="str">
+        <v>106</v>
+      </c>
+      <c r="C24" t="str">
+        <v/>
+      </c>
+      <c r="D24" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E24" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F24" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>HD-HCM-ROOM-RENO-01</v>
+      </c>
+      <c r="B25" t="str">
+        <v>107</v>
+      </c>
+      <c r="C25" t="str">
+        <v/>
+      </c>
+      <c r="D25" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E25" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F25" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>HD-HCM-ROOM-RENO-01</v>
+      </c>
+      <c r="B26" t="str">
+        <v>108</v>
+      </c>
+      <c r="C26" t="str">
+        <v/>
+      </c>
+      <c r="D26" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E26" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F26" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>HD-HCM-ROOM-NORENO-01</v>
+      </c>
+      <c r="B27" t="str">
+        <v>103</v>
+      </c>
+      <c r="C27" t="str">
+        <v/>
+      </c>
+      <c r="D27" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E27" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F27" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>HD-HCM-ROOM-NORENO-01</v>
+      </c>
+      <c r="B28" t="str">
+        <v>104</v>
+      </c>
+      <c r="C28" t="str">
+        <v/>
+      </c>
+      <c r="D28" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E28" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F28" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>HD-HCM-ROOM-NORENO-01</v>
+      </c>
+      <c r="B29" t="str">
+        <v>105</v>
+      </c>
+      <c r="C29" t="str">
+        <v/>
+      </c>
+      <c r="D29" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E29" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F29" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>HD-HCM-ROOM-NORENO-01</v>
+      </c>
+      <c r="B30" t="str">
+        <v>106</v>
+      </c>
+      <c r="C30" t="str">
+        <v/>
+      </c>
+      <c r="D30" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E30" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F30" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>HD-HN-ROOM-RENO-01</v>
+      </c>
+      <c r="B31" t="str">
+        <v>104</v>
+      </c>
+      <c r="C31" t="str">
+        <v/>
+      </c>
+      <c r="D31" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E31" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F31" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>HD-HN-ROOM-RENO-01</v>
+      </c>
+      <c r="B32" t="str">
+        <v>105</v>
+      </c>
+      <c r="C32" t="str">
+        <v/>
+      </c>
+      <c r="D32" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E32" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F32" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>HD-HN-ROOM-RENO-01</v>
+      </c>
+      <c r="B33" t="str">
+        <v>106</v>
+      </c>
+      <c r="C33" t="str">
+        <v/>
+      </c>
+      <c r="D33" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E33" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F33" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>HD-HN-ROOM-RENO-01</v>
+      </c>
+      <c r="B34" t="str">
+        <v>107</v>
+      </c>
+      <c r="C34" t="str">
+        <v/>
+      </c>
+      <c r="D34" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E34" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F34" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>HD-HN-ROOM-RENO-01</v>
+      </c>
+      <c r="B35" t="str">
+        <v>108</v>
+      </c>
+      <c r="C35" t="str">
+        <v/>
+      </c>
+      <c r="D35" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E35" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F35" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>HD-HN-ROOM-RENO-01</v>
+      </c>
+      <c r="B36" t="str">
+        <v>109</v>
+      </c>
+      <c r="C36" t="str">
+        <v/>
+      </c>
+      <c r="D36" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E36" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F36" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>HD-HN-ROOM-RENO-01</v>
+      </c>
+      <c r="B37" t="str">
+        <v>110</v>
+      </c>
+      <c r="C37" t="str">
+        <v/>
+      </c>
+      <c r="D37" t="str">
+        <v>Quạt</v>
+      </c>
+      <c r="E37" t="str">
+        <v>INITIAL_HANDOVER</v>
+      </c>
+      <c r="F37" t="str">
+        <v>GOOD</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37" t="str">
+        <v>Phòng trống — chưa lắp thiết bị riêng</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I37"/>
   </ignoredErrors>
 </worksheet>
 </file>